--- a/reports/jira_report.xlsx
+++ b/reports/jira_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,33 +519,6 @@
         </is>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PROJ-104</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dashboard Testing</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>

--- a/reports/jira_report.xlsx
+++ b/reports/jira_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,6 +523,29 @@
           <t>Low</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PROJ-104</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dashboard Testing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/jira_report.xlsx
+++ b/reports/jira_report.xlsx
@@ -473,61 +473,61 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PROJ-101</t>
+          <t>PROJ-104</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Login validation</t>
+          <t>Dashboard Testing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PROJ-103</t>
+          <t>PROJ-101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dashboard Testing</t>
+          <t>Login validation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>John</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROJ-104</t>
+          <t>PROJ-103</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,7 +545,11 @@
           <t>Sara</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
